--- a/labs/lab-06-reporting-skill/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-06-reporting-skill/data/Northstar_Work_Orders.xlsx
@@ -13,16 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'About_This_Data'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Work_Orders'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Technicians'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Control'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Prompt_Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Checks'!$A$1:$C$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -562,7 +556,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1332,7 +1325,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="4" t="n">
         <v>46278</v>
       </c>
@@ -1972,7 +1965,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="4" t="n">
         <v>46266</v>
       </c>
@@ -3260,7 +3253,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="4" t="n">
         <v>46242</v>
       </c>
@@ -4548,7 +4541,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="4" t="n">
         <v>46218</v>
       </c>
@@ -5188,7 +5181,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="4" t="n">
         <v>46286</v>
       </c>
@@ -6476,7 +6469,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2"/>
       <c r="G110" s="4" t="n">
         <v>46262</v>
       </c>
@@ -7091,7 +7084,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7297,7 +7289,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7479,7 +7470,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7646,7 +7636,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7690,12 +7679,10 @@
       </c>
       <c r="B2" s="2">
         <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7706,7 +7693,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_or_Test</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_and_Scope</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>As_At</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Verified_By</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -7771,35 +7830,104 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>## OUTPUT AND REVIEW</t>
+          <t>## DASHBOARD LAYOUT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
+          <t>Dashboard sheet: title in A1; Site, Job_Category, Status and Assigned_To dropdowns in B2:B5 (All plus source values); the six measures in B7:B12; data-as-at date and selected scope in D2.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
+          <t>Six KPI tiles in D4:I7, one column per tile: title in row 4, large value in row 5, short definition in row 6 and "Checks: PASS" in row 7.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Charts in a grid below the tiles: work orders by status and by job category side by side, then a full-width stacked bar by site (overdue backlog, other backlog, Closed, Cancelled).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Slicers for Site, Job_Category, Status and Assigned_To on the right of the tiles, connected to tblWorkOrders. KPI formulas use SUBTOTAL visibility so slicers and dropdowns both filter every tile and chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Put chart summaries, chart-title formulas and KPI checks on Dashboard_Summaries. Never merge cells. Hide gridlines on Dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>## DASHBOARD STYLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Tiles: white bold text on solid navy #1F4E79 (totals and rates), blue #2E75B6 (backlog, overdue) or teal #2A9D8F (Closed, cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Every chart title states the finding from a cell formula, e.g. "Changi Workshop has the most overdue backlog (18 of 50)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Show data labels on bars; no gridlines; rates as % with one decimal. Each chart total must equal B7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>## OUTPUT AND REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2">
+    <row r="23">
+      <c r="A23" s="2">
         <f>"Reporting date: "&amp;TEXT(Control!B2,"yyyy-mm-dd")</f>
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/labs/lab-06-reporting-skill/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-06-reporting-skill/data/Northstar_Work_Orders.xlsx
@@ -546,12 +546,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Rejoin</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>This input is a deterministic checkpoint, not proof of your Copilot output.</t>
+          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
         </is>
       </c>
     </row>

--- a/labs/lab-06-reporting-skill/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-06-reporting-skill/data/Northstar_Work_Orders.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
+          <t>Synthetic training data. Work on this file in your lab folder.</t>
         </is>
       </c>
     </row>
@@ -7531,76 +7531,72 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MICROSOFT 365 COPILOT WEB</t>
+          <t xml:space="preserve">OneDrive </t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MICROSOFT 365 COPILOT WEB:
-Write complete maintenance-reporting SKILL.md with YAML name/description. Require actual tblWorkOrders or a verified Word snapshot, report date and filter scope. Respect visible .Rules. Define backlog, overdue and Closed-only on-time rate. Preserve IDs/statuses/current owners; keep assignment proposals separate and approvals UNKNOWN. Create a verified Excel summary and improve a supplied four- or eight-slide PowerPoint report from selected evidence. Ask for missing inputs and before replacing only named outputs; rerun without duplicates or source changes. Keep the existing design and source/date notes. Never send email or approve assignments. Return the entire file.</t>
+          <t>OneDrive : Documents &gt; Copilot &gt; Microsoft Excel &gt; skills &gt; maintenance-reporting &gt; SKILL.md</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - PLAN</t>
+          <t xml:space="preserve">Check </t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - PLAN:
-@maintenance-reporting Build Maintenance_Summary for tblWorkOrders at 2026-09-30 with all filters All. Include total, closed, cancelled, backlog, overdue, on-time closed rate and recorded cost; show formulas and source scope. Plan first. Preserve source records.
-EXCEL - ALLOW EDITING:
-Apply that reviewed summary plan. Add Assignment_Proposals for unassigned backlog only. Use tblTechnicians primary category and available hours as planning inputs; show category/capacity checks, current owner and proposed owner separately. Leave manager decision UNKNOWN. Do not change Assigned_To.</t>
+          <t>Check : maintenance-reporting appears when you type @main</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Step 4</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - CHAT ONLY</t>
+          <t>EXCEL - ALLOW EDITING</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - CHAT ONLY:
-@maintenance-reporting Review Assignment_Proposals against tblWorkOrders and tblTechnicians. Check each suggested owner has the matching water-service job category, capacity limitations are visible and original Assigned_To values are unchanged. Leave manager approval UNKNOWN; do not assign or schedule a technician.</t>
+          <t>EXCEL - ALLOW EDITING:
+@maintenance-reporting Build a Maintenance_Summary sheet for 30 September 2026 with the total, closed, cancelled, backlog, overdue, on-time closure rate and cost.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>POWERPOINT COPILOT</t>
+          <t>EXCEL - ALLOW EDITING</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>POWERPOINT COPILOT:
-@maintenance-reporting Improve this existing four-slide Northstar update from the selected verified Word snapshot. Preserve slide count, all values and source/date/scope notes; use clear claim headlines and the existing design. Keep assignment suggestions explicitly proposed and do not assume access to Excel chat.</t>
+          <t>EXCEL - ALLOW EDITING:
+@maintenance-reporting Add an Assignment_Proposals sheet for the backlog jobs with no owner. Suggest an owner from tblTechnicians with the same job category and free hours, and mark each one as a proposal. Don’t change Assigned_To.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Step 6</t>
+          <t>Step 5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -7611,27 +7607,25 @@
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>EXCEL - CHAT ONLY:
-@maintenance-reporting Prepare my next maintenance report. I need a DIFFERENT reporting period from the course example and have not supplied any source, date or scope. This empty workbook contains no work orders. Tell me what you need; do not invent data.
-EXCEL - PLAN:
-@maintenance-reporting Rebuild the existing Maintenance_Summary for the same table, date and scope. Describe what will be replaced, ask before replacement and keep source/unrelated sheets. Do not duplicate outputs.</t>
+@maintenance-reporting Prepare my maintenance report for last month.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Step 7</t>
+          <t>Step 6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MICROSOFT 365 COPILOT WEB</t>
+          <t>POWERPOINT COPILOT</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>MICROSOFT 365 COPILOT WEB:
-Improve this supplied maintenance-reporting skill to v2 using only my actual smoke-test and rerun findings pasted here. Add explicit missing-input and no-duplicate-output guards. Keep Excel source and current owners protected. Return the complete revised SKILL.md and a short before/after change log; do not fabricate test evidence.</t>
+          <t>POWERPOINT COPILOT:
+@maintenance-reporting Improve these 4 slides with clearer headlines and less text. Keep every number and keep 4 slides.</t>
         </is>
       </c>
     </row>

--- a/labs/lab-06-reporting-skill/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-06-reporting-skill/data/Northstar_Work_Orders.xlsx
@@ -155,9 +155,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblWorkOrders" displayName="tblWorkOrders" ref="A1:M121" headerRowCount="1">
-  <autoFilter ref="A1:M121"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblWorkOrders" displayName="tblWorkOrders" ref="A1:N121" headerRowCount="1">
+  <autoFilter ref="A1:N121"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="Work_Order_ID"/>
     <tableColumn id="2" name="Site"/>
     <tableColumn id="3" name="Job_Category"/>
@@ -171,6 +171,7 @@
     <tableColumn id="11" name="Actual_Hours"/>
     <tableColumn id="12" name="Cost_SGD"/>
     <tableColumn id="13" name="Description"/>
+    <tableColumn id="14" name="Failure_Mode"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -566,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -582,6 +583,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,6 +652,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Failure_Mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -705,6 +712,11 @@
           <t>Leak Repair scheduled or reactive task 001</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -758,6 +770,11 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 002</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -813,6 +830,11 @@
           <t>Leak Repair scheduled or reactive task 003</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -866,6 +888,11 @@
           <t>Leak Repair scheduled or reactive task 004</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -919,6 +946,11 @@
           <t>Valve Repair scheduled or reactive task 005</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -974,6 +1006,11 @@
           <t>Valve Repair scheduled or reactive task 006</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1027,6 +1064,11 @@
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 007</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -1082,6 +1124,11 @@
           <t>Valve Repair scheduled or reactive task 008</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1135,6 +1182,11 @@
           <t>Pipe Replacement scheduled or reactive task 009</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1188,6 +1240,11 @@
           <t>Pipe Replacement scheduled or reactive task 010</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1243,6 +1300,11 @@
           <t>Pipe Replacement scheduled or reactive task 011</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1296,6 +1358,11 @@
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 012</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1347,6 +1414,11 @@
           <t>Pump Service scheduled or reactive task 013</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1400,6 +1472,11 @@
           <t>Pump Service scheduled or reactive task 014</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1453,6 +1530,11 @@
           <t>Pump Service scheduled or reactive task 015</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1508,6 +1590,11 @@
           <t>Pump Service scheduled or reactive task 016</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1561,6 +1648,11 @@
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 017</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1616,6 +1708,11 @@
           <t>Meter Service scheduled or reactive task 018</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1669,6 +1766,11 @@
           <t>Meter Service scheduled or reactive task 019</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1722,6 +1824,11 @@
           <t>Meter Service scheduled or reactive task 020</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1777,6 +1884,11 @@
           <t>Leak Repair scheduled or reactive task 021</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1830,6 +1942,11 @@
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 022</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1885,6 +2002,11 @@
           <t>Leak Repair scheduled or reactive task 023</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1938,6 +2060,11 @@
           <t>Leak Repair scheduled or reactive task 024</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1987,6 +2114,11 @@
           <t>Valve Repair scheduled or reactive task 025</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2042,6 +2174,11 @@
           <t>Valve Repair scheduled or reactive task 026</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2095,6 +2232,11 @@
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 027</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -2150,6 +2292,11 @@
           <t>Valve Repair scheduled or reactive task 028</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2203,6 +2350,11 @@
           <t>Pipe Replacement scheduled or reactive task 029</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2256,6 +2408,11 @@
           <t>Pipe Replacement scheduled or reactive task 030</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2311,6 +2468,11 @@
           <t>Pipe Replacement scheduled or reactive task 031</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2364,6 +2526,11 @@
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 032</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -2419,6 +2586,11 @@
           <t>Pump Service scheduled or reactive task 033</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2472,6 +2644,11 @@
           <t>Pump Service scheduled or reactive task 034</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2525,6 +2702,11 @@
           <t>Pump Service scheduled or reactive task 035</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2580,6 +2762,11 @@
           <t>Pump Service scheduled or reactive task 036</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2633,6 +2820,11 @@
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 037</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -2688,6 +2880,11 @@
           <t>Meter Service scheduled or reactive task 038</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2741,6 +2938,11 @@
           <t>Meter Service scheduled or reactive task 039</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2794,6 +2996,11 @@
           <t>Meter Service scheduled or reactive task 040</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2849,6 +3056,11 @@
           <t>Leak Repair scheduled or reactive task 041</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2902,6 +3114,11 @@
       <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 042</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -2957,6 +3174,11 @@
           <t>Leak Repair scheduled or reactive task 043</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3010,6 +3232,11 @@
           <t>Leak Repair scheduled or reactive task 044</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3063,6 +3290,11 @@
           <t>Valve Repair scheduled or reactive task 045</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3118,6 +3350,11 @@
           <t>Valve Repair scheduled or reactive task 046</t>
         </is>
       </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3171,6 +3408,11 @@
       <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 047</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
         </is>
       </c>
     </row>
@@ -3226,6 +3468,11 @@
           <t>Valve Repair scheduled or reactive task 048</t>
         </is>
       </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3275,6 +3522,11 @@
           <t>Pipe Replacement scheduled or reactive task 049</t>
         </is>
       </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3328,6 +3580,11 @@
           <t>Pipe Replacement scheduled or reactive task 050</t>
         </is>
       </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3383,6 +3640,11 @@
           <t>Pipe Replacement scheduled or reactive task 051</t>
         </is>
       </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3436,6 +3698,11 @@
       <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 052</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -3491,6 +3758,11 @@
           <t>Pump Service scheduled or reactive task 053</t>
         </is>
       </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3544,6 +3816,11 @@
           <t>Pump Service scheduled or reactive task 054</t>
         </is>
       </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3597,6 +3874,11 @@
           <t>Pump Service scheduled or reactive task 055</t>
         </is>
       </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3652,6 +3934,11 @@
           <t>Pump Service scheduled or reactive task 056</t>
         </is>
       </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3705,6 +3992,11 @@
       <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 057</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -3760,6 +4052,11 @@
           <t>Meter Service scheduled or reactive task 058</t>
         </is>
       </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3813,6 +4110,11 @@
           <t>Meter Service scheduled or reactive task 059</t>
         </is>
       </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3866,6 +4168,11 @@
           <t>Meter Service scheduled or reactive task 060</t>
         </is>
       </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3921,6 +4228,11 @@
           <t>Leak Repair scheduled or reactive task 061</t>
         </is>
       </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3974,6 +4286,11 @@
       <c r="M63" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 062</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -4029,6 +4346,11 @@
           <t>Leak Repair scheduled or reactive task 063</t>
         </is>
       </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4082,6 +4404,11 @@
           <t>Leak Repair scheduled or reactive task 064</t>
         </is>
       </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4135,6 +4462,11 @@
           <t>Valve Repair scheduled or reactive task 065</t>
         </is>
       </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4190,6 +4522,11 @@
           <t>Valve Repair scheduled or reactive task 066</t>
         </is>
       </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4243,6 +4580,11 @@
       <c r="M68" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 067</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -4298,6 +4640,11 @@
           <t>Valve Repair scheduled or reactive task 068</t>
         </is>
       </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4351,6 +4698,11 @@
           <t>Pipe Replacement scheduled or reactive task 069</t>
         </is>
       </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4404,6 +4756,11 @@
           <t>Pipe Replacement scheduled or reactive task 070</t>
         </is>
       </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4459,6 +4816,11 @@
           <t>Pipe Replacement scheduled or reactive task 071</t>
         </is>
       </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4512,6 +4874,11 @@
       <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 072</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -4563,6 +4930,11 @@
           <t>Pump Service scheduled or reactive task 073</t>
         </is>
       </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4616,6 +4988,11 @@
           <t>Pump Service scheduled or reactive task 074</t>
         </is>
       </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4669,6 +5046,11 @@
           <t>Pump Service scheduled or reactive task 075</t>
         </is>
       </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4724,6 +5106,11 @@
           <t>Pump Service scheduled or reactive task 076</t>
         </is>
       </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4777,6 +5164,11 @@
       <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 077</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -4832,6 +5224,11 @@
           <t>Meter Service scheduled or reactive task 078</t>
         </is>
       </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4885,6 +5282,11 @@
           <t>Meter Service scheduled or reactive task 079</t>
         </is>
       </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4938,6 +5340,11 @@
           <t>Meter Service scheduled or reactive task 080</t>
         </is>
       </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4993,6 +5400,11 @@
           <t>Leak Repair scheduled or reactive task 081</t>
         </is>
       </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5046,6 +5458,11 @@
       <c r="M83" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 082</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
         </is>
       </c>
     </row>
@@ -5101,6 +5518,11 @@
           <t>Leak Repair scheduled or reactive task 083</t>
         </is>
       </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5154,6 +5576,11 @@
           <t>Leak Repair scheduled or reactive task 084</t>
         </is>
       </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5203,6 +5630,11 @@
           <t>Valve Repair scheduled or reactive task 085</t>
         </is>
       </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5258,6 +5690,11 @@
           <t>Valve Repair scheduled or reactive task 086</t>
         </is>
       </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5311,6 +5748,11 @@
       <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 087</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -5366,6 +5808,11 @@
           <t>Valve Repair scheduled or reactive task 088</t>
         </is>
       </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5419,6 +5866,11 @@
           <t>Pipe Replacement scheduled or reactive task 089</t>
         </is>
       </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5472,6 +5924,11 @@
           <t>Pipe Replacement scheduled or reactive task 090</t>
         </is>
       </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5527,6 +5984,11 @@
           <t>Pipe Replacement scheduled or reactive task 091</t>
         </is>
       </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5580,6 +6042,11 @@
       <c r="M93" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 092</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -5635,6 +6102,11 @@
           <t>Pump Service scheduled or reactive task 093</t>
         </is>
       </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5688,6 +6160,11 @@
           <t>Pump Service scheduled or reactive task 094</t>
         </is>
       </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5741,6 +6218,11 @@
           <t>Pump Service scheduled or reactive task 095</t>
         </is>
       </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5796,6 +6278,11 @@
           <t>Pump Service scheduled or reactive task 096</t>
         </is>
       </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5849,6 +6336,11 @@
       <c r="M98" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 097</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -5904,6 +6396,11 @@
           <t>Meter Service scheduled or reactive task 098</t>
         </is>
       </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5957,6 +6454,11 @@
           <t>Meter Service scheduled or reactive task 099</t>
         </is>
       </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6010,6 +6512,11 @@
           <t>Meter Service scheduled or reactive task 100</t>
         </is>
       </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6065,6 +6572,11 @@
           <t>Leak Repair scheduled or reactive task 101</t>
         </is>
       </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6118,6 +6630,11 @@
       <c r="M103" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 102</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -6173,6 +6690,11 @@
           <t>Leak Repair scheduled or reactive task 103</t>
         </is>
       </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6226,6 +6748,11 @@
           <t>Leak Repair scheduled or reactive task 104</t>
         </is>
       </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6279,6 +6806,11 @@
           <t>Valve Repair scheduled or reactive task 105</t>
         </is>
       </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6334,6 +6866,11 @@
           <t>Valve Repair scheduled or reactive task 106</t>
         </is>
       </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6387,6 +6924,11 @@
       <c r="M108" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 107</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -6442,6 +6984,11 @@
           <t>Valve Repair scheduled or reactive task 108</t>
         </is>
       </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6491,6 +7038,11 @@
           <t>Pipe Replacement scheduled or reactive task 109</t>
         </is>
       </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6544,6 +7096,11 @@
           <t>Pipe Replacement scheduled or reactive task 110</t>
         </is>
       </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6599,6 +7156,11 @@
           <t>Pipe Replacement scheduled or reactive task 111</t>
         </is>
       </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6652,6 +7214,11 @@
       <c r="M113" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 112</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -6707,6 +7274,11 @@
           <t>Pump Service scheduled or reactive task 113</t>
         </is>
       </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6760,6 +7332,11 @@
           <t>Pump Service scheduled or reactive task 114</t>
         </is>
       </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6813,6 +7390,11 @@
           <t>Pump Service scheduled or reactive task 115</t>
         </is>
       </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6868,6 +7450,11 @@
           <t>Pump Service scheduled or reactive task 116</t>
         </is>
       </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6921,6 +7508,11 @@
       <c r="M118" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 117</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
         </is>
       </c>
     </row>
@@ -6976,6 +7568,11 @@
           <t>Meter Service scheduled or reactive task 118</t>
         </is>
       </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7029,6 +7626,11 @@
           <t>Meter Service scheduled or reactive task 119</t>
         </is>
       </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7080,6 +7682,11 @@
       <c r="M121" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 120</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -7536,7 +8143,8 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>OneDrive : Documents &gt; Copilot &gt; Microsoft Excel &gt; skills &gt; maintenance-reporting &gt; SKILL.md</t>
+          <t>OneDrive : Documents &gt; Copilot &gt; Microsoft Excel &gt; skills &gt; water-service-pareto &gt; SKILL.md
+OneDrive : Documents &gt; Copilot &gt; Microsoft Excel &gt; skills &gt; maintenance-reporting &gt; SKILL.md</t>
         </is>
       </c>
     </row>
@@ -7553,7 +8161,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Check : maintenance-reporting appears when you type @main</t>
+          <t>Check : water-service-pareto appears when you type @
+Check : maintenance-reporting appears when you type @</t>
         </is>
       </c>
     </row>
@@ -7589,7 +8198,7 @@
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>EXCEL - ALLOW EDITING:
-@maintenance-reporting Add an Assignment_Proposals sheet for the backlog jobs with no owner. Suggest an owner from tblTechnicians with the same job category and free hours, and mark each one as a proposal. Don’t change Assigned_To.</t>
+@water-service-pareto Make a Pareto chart of Failure_Mode for all work orders and place it on the Maintenance_Summary sheet, to the right of the numbers.</t>
         </is>
       </c>
     </row>
@@ -7601,13 +8210,13 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - CHAT ONLY</t>
+          <t>EXCEL - ALLOW EDITING</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - CHAT ONLY:
-@maintenance-reporting Prepare my maintenance report for last month.</t>
+          <t>EXCEL - ALLOW EDITING:
+@maintenance-reporting Add an Assignment_Proposals sheet for the backlog jobs with no owner. Suggest an owner from tblTechnicians with the same job category and free hours, and mark each one as a proposal. Don’t change Assigned_To.</t>
         </is>
       </c>
     </row>
